--- a/public/exports-with-coowners/41333014.xlsx
+++ b/public/exports-with-coowners/41333014.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-with-coowners/41333014.xlsx
+++ b/public/exports-with-coowners/41333014.xlsx
@@ -1616,7 +1616,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">H. C. Ørsteds Vej 2D</t>
+          <t xml:space="preserve">Rolstrupparken 1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">7927126</t>
+          <t xml:space="preserve">7896534</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1635,11 +1635,11 @@
         </is>
       </c>
       <c r="J22">
-        <v>653</v>
+        <v>453</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311110803</t>
+          <t xml:space="preserve">311110782</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolstrupparken 1</t>
+          <t xml:space="preserve">Rolstrupvej 10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">7896534</t>
+          <t xml:space="preserve">5568835</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1710,11 +1710,11 @@
         </is>
       </c>
       <c r="J23">
-        <v>453</v>
+        <v>764</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311110782</t>
+          <t xml:space="preserve">311112752</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2025-05-13</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolstrupvej 10</t>
+          <t xml:space="preserve">Næssundvej 325</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7960</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5568835</t>
+          <t xml:space="preserve">3442200</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1785,11 +1785,11 @@
         </is>
       </c>
       <c r="J24">
-        <v>764</v>
+        <v>1509</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311112752</t>
+          <t xml:space="preserve">311143918</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-13</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næssundvej 325</t>
+          <t xml:space="preserve">Skovparken 1A</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">3442200</t>
+          <t xml:space="preserve">5563842</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="J25">
-        <v>1509</v>
+        <v>949</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143918</t>
+          <t xml:space="preserve">311157673</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiConsult</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2026-02-08</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovparken 1A</t>
+          <t xml:space="preserve">Holgersgade 1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5563842</t>
+          <t xml:space="preserve">8283248</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1935,31 +1935,31 @@
         </is>
       </c>
       <c r="J26">
-        <v>949</v>
+        <v>1029</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311157673</t>
+          <t xml:space="preserve">311218644</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">EnergiConsult ApS</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-08</t>
+          <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holgersgade 1</t>
+          <t xml:space="preserve">Holgersgade 3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8283248</t>
+          <t xml:space="preserve">8741158</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2010,11 +2010,11 @@
         </is>
       </c>
       <c r="J27">
-        <v>1029</v>
+        <v>782</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218644</t>
+          <t xml:space="preserve">311218646</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morsø Kommune</t>
+          <t xml:space="preserve">Region Nordjylland</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holgersgade 3</t>
+          <t xml:space="preserve">Asylgade 25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8741158</t>
+          <t xml:space="preserve">8741160</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="J28">
-        <v>782</v>
+        <v>2702</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218646</t>
+          <t xml:space="preserve">311287323</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiConsult ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asylgade 25</t>
+          <t xml:space="preserve">Strandparken 48</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2151,20 +2151,20 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">8741160</t>
+          <t xml:space="preserve">5565403</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J29">
-        <v>2702</v>
+        <v>3011</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287323</t>
+          <t xml:space="preserve">311287415</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-05</t>
+          <t xml:space="preserve">2027-12-06</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2231,15 +2231,15 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J30">
-        <v>3011</v>
+        <v>956</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287415</t>
+          <t xml:space="preserve">311287416</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2306,15 +2306,15 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J31">
-        <v>956</v>
+        <v>1593</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287416</t>
+          <t xml:space="preserve">311287418</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region Nordjylland</t>
+          <t xml:space="preserve">Morsø Kommune</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2366,40 +2366,40 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandparken 48</t>
+          <t xml:space="preserve">Vindbakken 6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7970</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5565403</t>
+          <t xml:space="preserve">3444980</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J32">
-        <v>1593</v>
+        <v>1644</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287418</t>
+          <t xml:space="preserve">311291681</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">EnergiConsult ApS</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-06</t>
+          <t xml:space="preserve">2028-01-09</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindbakken 6</t>
+          <t xml:space="preserve">Riis Alle 33</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">7970</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3444980</t>
+          <t xml:space="preserve">100199383</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2460,11 +2460,11 @@
         </is>
       </c>
       <c r="J33">
-        <v>1644</v>
+        <v>3650</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291681</t>
+          <t xml:space="preserve">311511485</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-09</t>
+          <t xml:space="preserve">2031-04-12</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riis Alle 33</t>
+          <t xml:space="preserve">Skovgade 17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">100199383</t>
+          <t xml:space="preserve">5563837</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2535,11 +2535,11 @@
         </is>
       </c>
       <c r="J34">
-        <v>3650</v>
+        <v>916</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511485</t>
+          <t xml:space="preserve">311630222</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-12</t>
+          <t xml:space="preserve">2032-09-22</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovgade 17</t>
+          <t xml:space="preserve">Limfjordsvej 95A</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5563837</t>
+          <t xml:space="preserve">383950, 383951, 383952, 383953, 100226311</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2610,11 +2610,11 @@
         </is>
       </c>
       <c r="J35">
-        <v>916</v>
+        <v>12832</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311630222</t>
+          <t xml:space="preserve">311655787</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-22</t>
+          <t xml:space="preserve">2033-01-24</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Limfjordsvej 95A</t>
+          <t xml:space="preserve">Ringsgade 3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2676,20 +2676,20 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">383950, 383951, 383952, 383953, 100226311</t>
+          <t xml:space="preserve">5563951</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J36">
-        <v>12832</v>
+        <v>402</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655787</t>
+          <t xml:space="preserve">311689354</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-24</t>
+          <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringsgade 3</t>
+          <t xml:space="preserve">Nørrebro 140</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,20 +2751,20 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5563951</t>
+          <t xml:space="preserve">5566277</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J37">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689354</t>
+          <t xml:space="preserve">311773845</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-21</t>
+          <t xml:space="preserve">2034-07-17</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebro 140</t>
+          <t xml:space="preserve">Jernbanevej 5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5566277</t>
+          <t xml:space="preserve">8730510</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2835,11 +2835,11 @@
         </is>
       </c>
       <c r="J38">
-        <v>370</v>
+        <v>447</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311773845</t>
+          <t xml:space="preserve">311786989</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-17</t>
+          <t xml:space="preserve">2034-09-24</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 5</t>
+          <t xml:space="preserve">Jernbanevej 7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J39">
-        <v>447</v>
+        <v>5671</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 7</t>
+          <t xml:space="preserve">Tranevej 2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8730510</t>
+          <t xml:space="preserve">5568732</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2985,11 +2985,11 @@
         </is>
       </c>
       <c r="J40">
-        <v>5671</v>
+        <v>1128</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786989</t>
+          <t xml:space="preserve">311807701</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-24</t>
+          <t xml:space="preserve">2035-01-24</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tranevej 2</t>
+          <t xml:space="preserve">Duevej 9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5568732</t>
+          <t xml:space="preserve">5567529</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3060,11 +3060,11 @@
         </is>
       </c>
       <c r="J41">
-        <v>1128</v>
+        <v>9790</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311807701</t>
+          <t xml:space="preserve">311809736</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-24</t>
+          <t xml:space="preserve">2035-02-04</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duevej 9</t>
+          <t xml:space="preserve">Nygade 29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5567529</t>
+          <t xml:space="preserve">5563499</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3135,11 +3135,11 @@
         </is>
       </c>
       <c r="J42">
-        <v>9790</v>
+        <v>2577</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809736</t>
+          <t xml:space="preserve">311824434</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-04</t>
+          <t xml:space="preserve">2035-04-10</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 29</t>
+          <t xml:space="preserve">Støberivej 11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,20 +3201,20 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5563499</t>
+          <t xml:space="preserve">8802259</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J43">
-        <v>2577</v>
+        <v>1110</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824434</t>
+          <t xml:space="preserve">311827910</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-10</t>
+          <t xml:space="preserve">2035-04-29</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Støberivej 11</t>
+          <t xml:space="preserve">Støberivej 3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J44">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Støberivej 3</t>
+          <t xml:space="preserve">Støberivej 5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J45">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Støberivej 5</t>
+          <t xml:space="preserve">Støberivej 7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3431,15 +3431,15 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J46">
-        <v>1110</v>
+        <v>1186</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827910</t>
+          <t xml:space="preserve">311827787</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Støberivej 7</t>
+          <t xml:space="preserve">Støberivej 9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3506,15 +3506,15 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J47">
-        <v>1186</v>
+        <v>1110</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827787</t>
+          <t xml:space="preserve">311827910</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3566,30 +3566,30 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Støberivej 9</t>
+          <t xml:space="preserve">Poulsen Dalsvej 4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7950</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8802259</t>
+          <t xml:space="preserve">1429816</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J48">
-        <v>1110</v>
+        <v>5427</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827910</t>
+          <t xml:space="preserve">311840748</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-29</t>
+          <t xml:space="preserve">2035-06-25</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,30 +3641,30 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poulsen Dalsvej 4</t>
+          <t xml:space="preserve">Riis Alle 31D</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">7950</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429816</t>
+          <t xml:space="preserve">5567102</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J49">
-        <v>5427</v>
+        <v>293</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840748</t>
+          <t xml:space="preserve">311845015</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-25</t>
+          <t xml:space="preserve">2035-07-16</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riis Alle 31D</t>
+          <t xml:space="preserve">Riis Alle 31A</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3731,15 +3731,15 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J50">
-        <v>293</v>
+        <v>650</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311845015</t>
+          <t xml:space="preserve">311845194</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-16</t>
+          <t xml:space="preserve">2035-07-17</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riis Alle 31A</t>
+          <t xml:space="preserve">Riis Alle 31B</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J51">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riis Alle 31B</t>
+          <t xml:space="preserve">Riis Alle 31C</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3881,11 +3881,11 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J52">
-        <v>650</v>
+        <v>635</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riis Alle 31C</t>
+          <t xml:space="preserve">Rolstrupvej 1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,20 +3951,20 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5567102</t>
+          <t xml:space="preserve">9622609</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J53">
-        <v>635</v>
+        <v>3693</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311845194</t>
+          <t xml:space="preserve">311850483</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-17</t>
+          <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4016,30 +4016,30 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolstrupvej 1</t>
+          <t xml:space="preserve">Næssundvej 348A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7960</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9622609</t>
+          <t xml:space="preserve">3442077</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J54">
-        <v>3693</v>
+        <v>630</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850483</t>
+          <t xml:space="preserve">311851146</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-21</t>
+          <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næssundvej 348A</t>
+          <t xml:space="preserve">Næssundvej 348B</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4106,15 +4106,15 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J55">
-        <v>630</v>
+        <v>520</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851146</t>
+          <t xml:space="preserve">311851147</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næssundvej 348B</t>
+          <t xml:space="preserve">Næssundvej 348C</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J56">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næssundvej 348C</t>
+          <t xml:space="preserve">Næssundvej 348D</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J57">
@@ -4316,30 +4316,30 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næssundvej 348D</t>
+          <t xml:space="preserve">Elsøvej 240</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3442077</t>
+          <t xml:space="preserve">3441792</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J58">
-        <v>520</v>
+        <v>1569</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851147</t>
+          <t xml:space="preserve">311860707</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-25</t>
+          <t xml:space="preserve">2035-10-08</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsøvej 240</t>
+          <t xml:space="preserve">Bårupvej 15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7950</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3441792</t>
+          <t xml:space="preserve">3436575</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4410,11 +4410,11 @@
         </is>
       </c>
       <c r="J59">
-        <v>1569</v>
+        <v>1826</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311860707</t>
+          <t xml:space="preserve">311862116</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-08</t>
+          <t xml:space="preserve">2035-10-15</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,17 +4466,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bårupvej 15</t>
+          <t xml:space="preserve">Jernbanevej 9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">7950</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436575</t>
+          <t xml:space="preserve">5564812</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4485,11 +4485,11 @@
         </is>
       </c>
       <c r="J60">
-        <v>1826</v>
+        <v>562</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862116</t>
+          <t xml:space="preserve">311865986</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-15</t>
+          <t xml:space="preserve">2035-11-03</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 9</t>
+          <t xml:space="preserve">Skolestræde 11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5564812</t>
+          <t xml:space="preserve">3439180</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="J61">
-        <v>562</v>
+        <v>611</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865986</t>
+          <t xml:space="preserve">311866171</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-03</t>
+          <t xml:space="preserve">2035-11-04</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolestræde 11</t>
+          <t xml:space="preserve">Langebæksgade 34</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4626,20 +4626,20 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3439180</t>
+          <t xml:space="preserve">10130755</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J62">
-        <v>611</v>
+        <v>350</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866171</t>
+          <t xml:space="preserve">311868326</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-04</t>
+          <t xml:space="preserve">2035-11-14</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langebæksgade 34</t>
+          <t xml:space="preserve">Færøvej 1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,20 +4701,20 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">10130755</t>
+          <t xml:space="preserve">9066233</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J63">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868326</t>
+          <t xml:space="preserve">311868564</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-14</t>
+          <t xml:space="preserve">2035-11-17</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færøvej 1</t>
+          <t xml:space="preserve">Grønnegade 10A</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9066233</t>
+          <t xml:space="preserve">100003703</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4785,11 +4785,11 @@
         </is>
       </c>
       <c r="J64">
-        <v>1000</v>
+        <v>3187</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868564</t>
+          <t xml:space="preserve">311871957</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-17</t>
+          <t xml:space="preserve">2035-12-05</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4856,11 +4856,11 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J65">
-        <v>3187</v>
+        <v>1525</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -4931,11 +4931,11 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J66">
-        <v>1525</v>
+        <v>1920</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegade 10A</t>
+          <t xml:space="preserve">Lundkjærvej 22</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,20 +5001,20 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">100003703</t>
+          <t xml:space="preserve">5567939</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J67">
-        <v>1920</v>
+        <v>343</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871957</t>
+          <t xml:space="preserve">311873042</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-05</t>
+          <t xml:space="preserve">2035-12-11</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundkjærvej 22</t>
+          <t xml:space="preserve">Maagevej 60D</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5076,20 +5076,20 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5567939</t>
+          <t xml:space="preserve">5567560</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J68">
-        <v>343</v>
+        <v>262</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873042</t>
+          <t xml:space="preserve">311876821</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-11</t>
+          <t xml:space="preserve">2036-01-15</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maagevej 60D</t>
+          <t xml:space="preserve">Maagevej 60E</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,20 +5151,20 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5567560</t>
+          <t xml:space="preserve">8720449</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J69">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876821</t>
+          <t xml:space="preserve">311876820</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5216,30 +5216,30 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maagevej 60E</t>
+          <t xml:space="preserve">Smedebjergevej 49A</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7980</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8720449</t>
+          <t xml:space="preserve">3445792</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J70">
-        <v>297</v>
+        <v>366</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876820</t>
+          <t xml:space="preserve">311878772</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-15</t>
+          <t xml:space="preserve">2036-01-27</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,30 +5291,30 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedebjergevej 49A</t>
+          <t xml:space="preserve">Fyrvejen 65</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7980</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3445792</t>
+          <t xml:space="preserve">9743167</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J71">
-        <v>366</v>
+        <v>1658</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878772</t>
+          <t xml:space="preserve">311882494</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-27</t>
+          <t xml:space="preserve">2036-02-17</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fyrvejen 65</t>
+          <t xml:space="preserve">Holgersgade 5A</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9743167</t>
+          <t xml:space="preserve">8741159</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5385,11 +5385,11 @@
         </is>
       </c>
       <c r="J72">
-        <v>1658</v>
+        <v>1542</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882494</t>
+          <t xml:space="preserve">311883270</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-17</t>
+          <t xml:space="preserve">2036-02-20</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,17 +5441,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holgersgade 5A</t>
+          <t xml:space="preserve">Doktor Lunds Vej 3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7950</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">8741159</t>
+          <t xml:space="preserve">100055624</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="J73">
-        <v>1542</v>
+        <v>2292</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883270</t>
+          <t xml:space="preserve">311906511</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiConsult ApS</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-20</t>
+          <t xml:space="preserve">2036-06-08</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,17 +5516,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doktor Lunds Vej 3</t>
+          <t xml:space="preserve">Øroddevej 15</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">7950</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">100055624</t>
+          <t xml:space="preserve">5566050</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5535,21 +5535,21 @@
         </is>
       </c>
       <c r="J74">
-        <v>2292</v>
+        <v>972</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311906511</t>
+          <t xml:space="preserve">311909858</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">EnergiConsult ApS</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-08</t>
+          <t xml:space="preserve">2036-06-22</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øroddevej 15</t>
+          <t xml:space="preserve">Holmen 3</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,20 +5601,20 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5566050</t>
+          <t xml:space="preserve">10045441</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J75">
-        <v>972</v>
+        <v>432</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311909858</t>
+          <t xml:space="preserve">311916673</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-22</t>
+          <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmen 3</t>
+          <t xml:space="preserve">Lupinvej 7A</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,20 +5676,20 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">10045441</t>
+          <t xml:space="preserve">7797589</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J76">
-        <v>432</v>
+        <v>260</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916673</t>
+          <t xml:space="preserve">311918686</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-30</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lupinvej 7A</t>
+          <t xml:space="preserve">Lupinvej 7B</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5756,11 +5756,11 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J77">
-        <v>260</v>
+        <v>960</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lupinvej 7B</t>
+          <t xml:space="preserve">Lupinvej 7D</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5831,11 +5831,11 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J78">
-        <v>960</v>
+        <v>883</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lupinvej 7D</t>
+          <t xml:space="preserve">H. C. Ørsteds Vej 2D</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,20 +5901,20 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">7797589</t>
+          <t xml:space="preserve">7927126</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J79">
-        <v>883</v>
+        <v>653</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918686</t>
+          <t xml:space="preserve">311926925</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
